--- a/artfynd/S 3695-2023 artfynd.xlsx
+++ b/artfynd/S 3695-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -931,57 +931,55 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3490778</v>
+        <v>137103600</v>
       </c>
       <c r="B4" t="n">
-        <v>106813</v>
+        <v>80598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällebo, Vstm</t>
+          <t>Hällabomossen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498208</v>
+        <v>498292</v>
       </c>
       <c r="R4" t="n">
-        <v>6621429</v>
+        <v>6621598</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,17 +1003,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2010-09-07</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2010-09-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca. 75 Askar i en igenväxt beteshage. Asken är det dominerande trädet på vissa ställen i hagen. Här växer även lind, lönn, rönn, asp och hassel.</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,27 +1017,144 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Igenväxt betesmark</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Jansson</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Jansson</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137103600</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3490778</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hällebo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>498208</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6621429</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2010-09-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2010-09-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca. 75 Askar i en igenväxt beteshage. Asken är det dominerande trädet på vissa ställen i hagen. Här växer även lind, lönn, rönn, asp och hassel.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Igenväxt betesmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Jansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Jansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/3490778</t>
         </is>
@@ -1055,6 +1165,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3695-2023 artfynd.xlsx
+++ b/artfynd/S 3695-2023 artfynd.xlsx
@@ -934,7 +934,7 @@
         <v>137103600</v>
       </c>
       <c r="B4" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 3695-2023 artfynd.xlsx
+++ b/artfynd/S 3695-2023 artfynd.xlsx
@@ -934,7 +934,7 @@
         <v>137103600</v>
       </c>
       <c r="B4" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 3695-2023 artfynd.xlsx
+++ b/artfynd/S 3695-2023 artfynd.xlsx
@@ -934,7 +934,7 @@
         <v>137103600</v>
       </c>
       <c r="B4" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 3695-2023 artfynd.xlsx
+++ b/artfynd/S 3695-2023 artfynd.xlsx
@@ -934,7 +934,7 @@
         <v>137103600</v>
       </c>
       <c r="B4" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 3695-2023 artfynd.xlsx
+++ b/artfynd/S 3695-2023 artfynd.xlsx
@@ -934,7 +934,7 @@
         <v>137103600</v>
       </c>
       <c r="B4" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 3695-2023 artfynd.xlsx
+++ b/artfynd/S 3695-2023 artfynd.xlsx
@@ -934,7 +934,7 @@
         <v>137103600</v>
       </c>
       <c r="B4" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 3695-2023 artfynd.xlsx
+++ b/artfynd/S 3695-2023 artfynd.xlsx
@@ -934,7 +934,7 @@
         <v>137103600</v>
       </c>
       <c r="B4" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 3695-2023 artfynd.xlsx
+++ b/artfynd/S 3695-2023 artfynd.xlsx
@@ -934,7 +934,7 @@
         <v>137103600</v>
       </c>
       <c r="B4" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 3695-2023 artfynd.xlsx
+++ b/artfynd/S 3695-2023 artfynd.xlsx
@@ -934,7 +934,7 @@
         <v>137103600</v>
       </c>
       <c r="B4" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 3695-2023 artfynd.xlsx
+++ b/artfynd/S 3695-2023 artfynd.xlsx
@@ -934,7 +934,7 @@
         <v>137103600</v>
       </c>
       <c r="B4" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 3695-2023 artfynd.xlsx
+++ b/artfynd/S 3695-2023 artfynd.xlsx
@@ -934,7 +934,7 @@
         <v>137103600</v>
       </c>
       <c r="B4" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
